--- a/docs/StructureDefinition-DIPSRelatedPerson.xlsx
+++ b/docs/StructureDefinition-DIPSRelatedPerson.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7757" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7757" uniqueCount="801">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:16:58+00:00</t>
+    <t>2026-09-08T11:30:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -440,7 +440,7 @@
     <t>kinship</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSRelatedPersonKinship}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSRelatedPersonKinship}
 </t>
   </si>
   <si>
@@ -460,7 +460,7 @@
     <t>parentalResponsibility</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSRelatedPersonParentalResponsibility}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSRelatedPersonParentalResponsibility}
 </t>
   </si>
   <si>
@@ -470,7 +470,7 @@
     <t>appointedByMunicipality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSRelatedPersonAppointedByMunicipality}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSRelatedPersonAppointedByMunicipality}
 </t>
   </si>
   <si>
@@ -523,7 +523,7 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSRelatedPersonAppointedByMunicipality</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSRelatedPersonAppointedByMunicipality</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -591,6 +591,9 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSRelatedPersonAppointedByMunicipality</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -709,7 +712,7 @@
     <t>responsibleRequisitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSRelatedPersonResponsibleRequisitioner}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSRelatedPersonResponsibleRequisitioner}
 </t>
   </si>
   <si>
@@ -719,7 +722,7 @@
     <t>additionalInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSRelatedPersonAdditionalInformation}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSRelatedPersonAdditionalInformation}
 </t>
   </si>
   <si>
@@ -2204,7 +2207,7 @@
     <t>municipalityCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/MunicipalityCode}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/MunicipalityCode}
 </t>
   </si>
   <si>
@@ -4894,7 +4897,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>74</v>
@@ -4936,7 +4939,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -4951,21 +4954,21 @@
         <v>95</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4991,13 +4994,13 @@
         <v>149</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -5047,7 +5050,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -5062,21 +5065,21 @@
         <v>95</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5102,14 +5105,14 @@
         <v>103</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>74</v>
@@ -5158,7 +5161,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -5173,21 +5176,21 @@
         <v>95</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5213,14 +5216,14 @@
         <v>149</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>74</v>
@@ -5269,7 +5272,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -5284,21 +5287,21 @@
         <v>95</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5321,19 +5324,19 @@
         <v>84</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>74</v>
@@ -5382,7 +5385,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -5397,24 +5400,24 @@
         <v>95</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>127</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>74</v>
@@ -5436,7 +5439,7 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>138</v>
@@ -5519,13 +5522,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>127</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>74</v>
@@ -5547,7 +5550,7 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>138</v>
@@ -5630,10 +5633,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5659,16 +5662,16 @@
         <v>128</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>178</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>74</v>
@@ -5717,7 +5720,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -5743,10 +5746,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5769,17 +5772,17 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>74</v>
@@ -5816,7 +5819,7 @@
         <v>74</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
@@ -5826,7 +5829,7 @@
         <v>132</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -5841,24 +5844,24 @@
         <v>95</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>74</v>
@@ -5880,17 +5883,17 @@
         <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>74</v>
@@ -5939,7 +5942,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -5954,21 +5957,21 @@
         <v>95</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6074,10 +6077,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6185,10 +6188,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6214,16 +6217,16 @@
         <v>103</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>74</v>
@@ -6248,13 +6251,13 @@
         <v>74</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>74</v>
@@ -6272,7 +6275,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -6287,7 +6290,7 @@
         <v>95</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>74</v>
@@ -6298,10 +6301,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6324,19 +6327,19 @@
         <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>74</v>
@@ -6361,13 +6364,13 @@
         <v>74</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -6385,7 +6388,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -6400,21 +6403,21 @@
         <v>95</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6440,29 +6443,29 @@
         <v>97</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>74</v>
@@ -6498,7 +6501,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -6513,25 +6516,25 @@
         <v>95</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6553,13 +6556,13 @@
         <v>149</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6573,7 +6576,7 @@
         <v>74</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>74</v>
@@ -6609,7 +6612,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -6624,21 +6627,21 @@
         <v>95</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6661,13 +6664,13 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6718,7 +6721,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -6733,21 +6736,21 @@
         <v>95</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6770,16 +6773,16 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6829,7 +6832,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -6844,24 +6847,24 @@
         <v>95</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>74</v>
@@ -6883,17 +6886,17 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -6942,7 +6945,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -6957,21 +6960,21 @@
         <v>95</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7077,10 +7080,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7188,10 +7191,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7217,16 +7220,16 @@
         <v>103</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
@@ -7251,13 +7254,13 @@
         <v>74</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>74</v>
@@ -7275,7 +7278,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -7290,7 +7293,7 @@
         <v>95</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>74</v>
@@ -7301,10 +7304,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7327,19 +7330,19 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>74</v>
@@ -7364,13 +7367,13 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>74</v>
@@ -7388,7 +7391,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -7403,21 +7406,21 @@
         <v>95</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7443,29 +7446,29 @@
         <v>97</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>74</v>
@@ -7501,7 +7504,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -7516,25 +7519,25 @@
         <v>95</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7556,13 +7559,13 @@
         <v>149</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7576,7 +7579,7 @@
         <v>74</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>74</v>
@@ -7612,7 +7615,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -7627,21 +7630,21 @@
         <v>95</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7664,13 +7667,13 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7721,7 +7724,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -7736,21 +7739,21 @@
         <v>95</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7773,16 +7776,16 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7832,7 +7835,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -7847,24 +7850,24 @@
         <v>95</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>74</v>
@@ -7886,17 +7889,17 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
@@ -7945,7 +7948,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -7960,21 +7963,21 @@
         <v>95</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8080,10 +8083,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8191,10 +8194,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8220,16 +8223,16 @@
         <v>103</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>74</v>
@@ -8254,13 +8257,13 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -8278,7 +8281,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -8293,7 +8296,7 @@
         <v>95</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>74</v>
@@ -8304,10 +8307,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8330,19 +8333,19 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>74</v>
@@ -8367,13 +8370,13 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -8391,7 +8394,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -8406,21 +8409,21 @@
         <v>95</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8446,29 +8449,29 @@
         <v>97</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>74</v>
@@ -8504,7 +8507,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -8519,21 +8522,21 @@
         <v>95</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8559,13 +8562,13 @@
         <v>149</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8579,7 +8582,7 @@
         <v>74</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>74</v>
@@ -8615,7 +8618,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -8630,21 +8633,21 @@
         <v>95</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8667,13 +8670,13 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8724,7 +8727,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -8739,21 +8742,21 @@
         <v>95</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8776,16 +8779,16 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8835,7 +8838,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -8850,24 +8853,24 @@
         <v>95</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>74</v>
@@ -8889,17 +8892,17 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>74</v>
@@ -8948,7 +8951,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
@@ -8963,21 +8966,21 @@
         <v>95</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9083,10 +9086,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9194,10 +9197,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9223,16 +9226,16 @@
         <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>74</v>
@@ -9257,13 +9260,13 @@
         <v>74</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>74</v>
@@ -9281,7 +9284,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -9296,7 +9299,7 @@
         <v>95</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>74</v>
@@ -9307,10 +9310,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9333,19 +9336,19 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>74</v>
@@ -9370,13 +9373,13 @@
         <v>74</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -9394,7 +9397,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -9409,21 +9412,21 @@
         <v>95</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9449,29 +9452,29 @@
         <v>97</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>74</v>
@@ -9507,7 +9510,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -9522,21 +9525,21 @@
         <v>95</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9562,13 +9565,13 @@
         <v>149</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9582,7 +9585,7 @@
         <v>74</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="U61" t="s" s="2">
         <v>74</v>
@@ -9618,7 +9621,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -9633,21 +9636,21 @@
         <v>95</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9670,13 +9673,13 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9727,7 +9730,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
@@ -9742,21 +9745,21 @@
         <v>95</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9779,16 +9782,16 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9838,7 +9841,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -9853,21 +9856,21 @@
         <v>95</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9890,70 +9893,70 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q64" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="R64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q64" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="R64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -9968,10 +9971,10 @@
         <v>95</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>74</v>
@@ -9979,10 +9982,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10005,17 +10008,17 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>74</v>
@@ -10064,7 +10067,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -10079,21 +10082,21 @@
         <v>95</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10116,17 +10119,17 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>74</v>
@@ -10154,16 +10157,16 @@
         <v>107</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
@@ -10173,7 +10176,7 @@
         <v>132</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -10188,27 +10191,27 @@
         <v>95</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10227,17 +10230,17 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>74</v>
@@ -10262,11 +10265,11 @@
         <v>74</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>74</v>
@@ -10284,7 +10287,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
@@ -10299,21 +10302,21 @@
         <v>95</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10419,10 +10422,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10530,10 +10533,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10559,16 +10562,16 @@
         <v>167</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>74</v>
@@ -10617,7 +10620,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -10632,21 +10635,21 @@
         <v>95</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10752,10 +10755,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10863,10 +10866,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10908,7 +10911,7 @@
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>74</v>
@@ -10950,7 +10953,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -10965,21 +10968,21 @@
         <v>95</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11005,13 +11008,13 @@
         <v>149</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11061,7 +11064,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
@@ -11076,21 +11079,21 @@
         <v>95</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11116,14 +11119,14 @@
         <v>103</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>74</v>
@@ -11172,7 +11175,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
@@ -11187,21 +11190,21 @@
         <v>95</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11227,14 +11230,14 @@
         <v>149</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>74</v>
@@ -11283,7 +11286,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
@@ -11298,21 +11301,21 @@
         <v>95</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11335,19 +11338,19 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>74</v>
@@ -11396,7 +11399,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
@@ -11411,21 +11414,21 @@
         <v>95</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11451,16 +11454,16 @@
         <v>149</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>74</v>
@@ -11509,7 +11512,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -11524,27 +11527,27 @@
         <v>95</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11563,17 +11566,17 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>74</v>
@@ -11598,11 +11601,11 @@
         <v>74</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -11620,7 +11623,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
@@ -11635,21 +11638,21 @@
         <v>95</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11755,10 +11758,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11866,10 +11869,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11895,16 +11898,16 @@
         <v>167</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>74</v>
@@ -11953,7 +11956,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>75</v>
@@ -11968,21 +11971,21 @@
         <v>95</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12088,10 +12091,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12199,10 +12202,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12244,7 +12247,7 @@
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>74</v>
@@ -12286,7 +12289,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
@@ -12301,21 +12304,21 @@
         <v>95</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12341,13 +12344,13 @@
         <v>149</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12397,7 +12400,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
@@ -12412,21 +12415,21 @@
         <v>95</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12452,14 +12455,14 @@
         <v>103</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>74</v>
@@ -12508,7 +12511,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>75</v>
@@ -12523,21 +12526,21 @@
         <v>95</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12563,14 +12566,14 @@
         <v>149</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>74</v>
@@ -12619,7 +12622,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
@@ -12634,21 +12637,21 @@
         <v>95</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12671,19 +12674,19 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>74</v>
@@ -12732,7 +12735,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -12747,21 +12750,21 @@
         <v>95</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12787,16 +12790,16 @@
         <v>149</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>74</v>
@@ -12845,7 +12848,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
@@ -12860,27 +12863,27 @@
         <v>95</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12899,17 +12902,17 @@
         <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>74</v>
@@ -12934,11 +12937,11 @@
         <v>74</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>74</v>
@@ -12956,7 +12959,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
@@ -12971,21 +12974,21 @@
         <v>95</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13091,10 +13094,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13202,10 +13205,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13231,16 +13234,16 @@
         <v>167</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>74</v>
@@ -13289,7 +13292,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -13304,21 +13307,21 @@
         <v>95</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13424,10 +13427,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13535,10 +13538,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13580,7 +13583,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>74</v>
@@ -13622,7 +13625,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>75</v>
@@ -13637,21 +13640,21 @@
         <v>95</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13677,13 +13680,13 @@
         <v>149</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13733,7 +13736,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>75</v>
@@ -13748,21 +13751,21 @@
         <v>95</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13788,14 +13791,14 @@
         <v>103</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>74</v>
@@ -13844,7 +13847,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>75</v>
@@ -13859,21 +13862,21 @@
         <v>95</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13899,14 +13902,14 @@
         <v>149</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>74</v>
@@ -13955,7 +13958,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
@@ -13970,21 +13973,21 @@
         <v>95</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14007,19 +14010,19 @@
         <v>84</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>74</v>
@@ -14068,7 +14071,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
@@ -14083,21 +14086,21 @@
         <v>95</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14123,16 +14126,16 @@
         <v>149</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>74</v>
@@ -14181,7 +14184,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
@@ -14196,24 +14199,24 @@
         <v>95</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>74</v>
@@ -14235,17 +14238,17 @@
         <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>74</v>
@@ -14273,10 +14276,10 @@
         <v>107</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>74</v>
@@ -14294,7 +14297,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>75</v>
@@ -14309,21 +14312,21 @@
         <v>95</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14429,10 +14432,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14540,10 +14543,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14569,16 +14572,16 @@
         <v>167</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>74</v>
@@ -14627,7 +14630,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -14642,21 +14645,21 @@
         <v>95</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14762,10 +14765,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14873,10 +14876,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14918,7 +14921,7 @@
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>74</v>
@@ -14960,7 +14963,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>75</v>
@@ -14975,21 +14978,21 @@
         <v>95</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15015,13 +15018,13 @@
         <v>149</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15071,7 +15074,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>75</v>
@@ -15086,21 +15089,21 @@
         <v>95</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15126,14 +15129,14 @@
         <v>103</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>74</v>
@@ -15182,7 +15185,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>75</v>
@@ -15197,21 +15200,21 @@
         <v>95</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15237,14 +15240,14 @@
         <v>149</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>74</v>
@@ -15293,7 +15296,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>75</v>
@@ -15308,21 +15311,21 @@
         <v>95</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15345,19 +15348,19 @@
         <v>84</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>74</v>
@@ -15406,7 +15409,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>75</v>
@@ -15421,21 +15424,21 @@
         <v>95</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15461,16 +15464,16 @@
         <v>149</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>74</v>
@@ -15519,7 +15522,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>75</v>
@@ -15534,24 +15537,24 @@
         <v>95</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>74</v>
@@ -15573,17 +15576,17 @@
         <v>84</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>74</v>
@@ -15611,10 +15614,10 @@
         <v>107</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>74</v>
@@ -15632,7 +15635,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>75</v>
@@ -15647,21 +15650,21 @@
         <v>95</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15767,10 +15770,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15878,10 +15881,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15907,16 +15910,16 @@
         <v>167</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>74</v>
@@ -15965,7 +15968,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>75</v>
@@ -15980,21 +15983,21 @@
         <v>95</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16100,10 +16103,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16211,10 +16214,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16256,7 +16259,7 @@
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>74</v>
@@ -16298,7 +16301,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>75</v>
@@ -16313,21 +16316,21 @@
         <v>95</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16353,13 +16356,13 @@
         <v>149</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16409,7 +16412,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>75</v>
@@ -16424,21 +16427,21 @@
         <v>95</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16464,14 +16467,14 @@
         <v>103</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>74</v>
@@ -16520,7 +16523,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>75</v>
@@ -16535,21 +16538,21 @@
         <v>95</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16575,14 +16578,14 @@
         <v>149</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>74</v>
@@ -16631,7 +16634,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>75</v>
@@ -16646,21 +16649,21 @@
         <v>95</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16683,19 +16686,19 @@
         <v>84</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>74</v>
@@ -16744,7 +16747,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>75</v>
@@ -16759,21 +16762,21 @@
         <v>95</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16799,16 +16802,16 @@
         <v>149</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>74</v>
@@ -16857,7 +16860,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>75</v>
@@ -16872,24 +16875,24 @@
         <v>95</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>74</v>
@@ -16911,17 +16914,17 @@
         <v>84</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>74</v>
@@ -16949,10 +16952,10 @@
         <v>107</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>74</v>
@@ -16970,7 +16973,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>75</v>
@@ -16985,21 +16988,21 @@
         <v>95</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17105,10 +17108,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17216,10 +17219,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17245,16 +17248,16 @@
         <v>167</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>74</v>
@@ -17303,7 +17306,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>75</v>
@@ -17318,21 +17321,21 @@
         <v>95</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17438,10 +17441,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17549,10 +17552,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17594,7 +17597,7 @@
       </c>
       <c r="Q133" s="2"/>
       <c r="R133" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="S133" t="s" s="2">
         <v>74</v>
@@ -17636,7 +17639,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>75</v>
@@ -17651,21 +17654,21 @@
         <v>95</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17691,13 +17694,13 @@
         <v>149</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17747,7 +17750,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>75</v>
@@ -17762,21 +17765,21 @@
         <v>95</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17802,14 +17805,14 @@
         <v>103</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>74</v>
@@ -17858,7 +17861,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>75</v>
@@ -17873,21 +17876,21 @@
         <v>95</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17913,14 +17916,14 @@
         <v>149</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>74</v>
@@ -17969,7 +17972,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>75</v>
@@ -17984,21 +17987,21 @@
         <v>95</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18021,19 +18024,19 @@
         <v>84</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>74</v>
@@ -18082,7 +18085,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>75</v>
@@ -18097,21 +18100,21 @@
         <v>95</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18137,16 +18140,16 @@
         <v>149</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>74</v>
@@ -18195,7 +18198,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>75</v>
@@ -18210,24 +18213,24 @@
         <v>95</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>74</v>
@@ -18249,17 +18252,17 @@
         <v>84</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>74</v>
@@ -18287,10 +18290,10 @@
         <v>107</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>74</v>
@@ -18308,7 +18311,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>75</v>
@@ -18323,21 +18326,21 @@
         <v>95</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18443,10 +18446,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18554,10 +18557,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18583,16 +18586,16 @@
         <v>167</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>74</v>
@@ -18641,7 +18644,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>75</v>
@@ -18656,21 +18659,21 @@
         <v>95</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18776,10 +18779,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18887,10 +18890,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18932,7 +18935,7 @@
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>74</v>
@@ -18974,7 +18977,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>75</v>
@@ -18989,21 +18992,21 @@
         <v>95</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19029,13 +19032,13 @@
         <v>149</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -19085,7 +19088,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>75</v>
@@ -19100,21 +19103,21 @@
         <v>95</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19140,14 +19143,14 @@
         <v>103</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>74</v>
@@ -19196,7 +19199,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>75</v>
@@ -19211,21 +19214,21 @@
         <v>95</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19251,14 +19254,14 @@
         <v>149</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>74</v>
@@ -19307,7 +19310,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>75</v>
@@ -19322,21 +19325,21 @@
         <v>95</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19359,19 +19362,19 @@
         <v>84</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>74</v>
@@ -19420,7 +19423,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>75</v>
@@ -19435,21 +19438,21 @@
         <v>95</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19475,16 +19478,16 @@
         <v>149</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>74</v>
@@ -19533,7 +19536,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>75</v>
@@ -19548,24 +19551,24 @@
         <v>95</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>74</v>
@@ -19587,17 +19590,17 @@
         <v>84</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>74</v>
@@ -19625,10 +19628,10 @@
         <v>107</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>74</v>
@@ -19646,7 +19649,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>75</v>
@@ -19661,21 +19664,21 @@
         <v>95</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19781,10 +19784,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19892,10 +19895,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19921,16 +19924,16 @@
         <v>167</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>74</v>
@@ -19979,7 +19982,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>75</v>
@@ -19994,21 +19997,21 @@
         <v>95</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20114,10 +20117,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20225,10 +20228,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20270,7 +20273,7 @@
       </c>
       <c r="Q157" s="2"/>
       <c r="R157" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="S157" t="s" s="2">
         <v>74</v>
@@ -20312,7 +20315,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>75</v>
@@ -20327,21 +20330,21 @@
         <v>95</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20367,13 +20370,13 @@
         <v>149</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -20423,7 +20426,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>75</v>
@@ -20438,21 +20441,21 @@
         <v>95</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20478,14 +20481,14 @@
         <v>103</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>74</v>
@@ -20534,7 +20537,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>75</v>
@@ -20549,21 +20552,21 @@
         <v>95</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20589,14 +20592,14 @@
         <v>149</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>74</v>
@@ -20645,7 +20648,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>75</v>
@@ -20660,21 +20663,21 @@
         <v>95</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20697,19 +20700,19 @@
         <v>84</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>74</v>
@@ -20758,7 +20761,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>75</v>
@@ -20773,21 +20776,21 @@
         <v>95</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20813,16 +20816,16 @@
         <v>149</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>74</v>
@@ -20871,7 +20874,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>75</v>
@@ -20886,21 +20889,21 @@
         <v>95</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20923,17 +20926,17 @@
         <v>84</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>74</v>
@@ -20982,7 +20985,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>75</v>
@@ -20997,21 +21000,21 @@
         <v>95</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21117,10 +21120,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21226,13 +21229,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B166" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="B166" t="s" s="2">
-        <v>537</v>
-      </c>
       <c r="C166" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D166" t="s" s="2">
         <v>74</v>
@@ -21254,13 +21257,13 @@
         <v>74</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -21337,10 +21340,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21366,16 +21369,16 @@
         <v>103</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>74</v>
@@ -21400,13 +21403,13 @@
         <v>74</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>74</v>
@@ -21424,7 +21427,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>75</v>
@@ -21439,21 +21442,21 @@
         <v>95</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21479,16 +21482,16 @@
         <v>149</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>74</v>
@@ -21537,7 +21540,7 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>75</v>
@@ -21552,25 +21555,25 @@
         <v>95</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -21592,13 +21595,13 @@
         <v>149</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -21648,7 +21651,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>75</v>
@@ -21663,25 +21666,25 @@
         <v>95</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
@@ -21703,13 +21706,13 @@
         <v>149</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -21759,7 +21762,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>75</v>
@@ -21774,21 +21777,21 @@
         <v>95</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21814,10 +21817,10 @@
         <v>149</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -21868,7 +21871,7 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>75</v>
@@ -21883,21 +21886,21 @@
         <v>95</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21923,10 +21926,10 @@
         <v>149</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -21977,7 +21980,7 @@
         <v>74</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>75</v>
@@ -21992,21 +21995,21 @@
         <v>95</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22029,17 +22032,17 @@
         <v>84</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>74</v>
@@ -22088,7 +22091,7 @@
         <v>74</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>75</v>
@@ -22103,21 +22106,21 @@
         <v>95</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22140,19 +22143,19 @@
         <v>84</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>74</v>
@@ -22201,7 +22204,7 @@
         <v>74</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>75</v>
@@ -22216,21 +22219,21 @@
         <v>95</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22256,14 +22259,14 @@
         <v>103</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>74</v>
@@ -22288,13 +22291,13 @@
         <v>74</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>74</v>
@@ -22312,7 +22315,7 @@
         <v>74</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>75</v>
@@ -22327,21 +22330,21 @@
         <v>95</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22364,13 +22367,13 @@
         <v>84</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -22421,7 +22424,7 @@
         <v>74</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>75</v>
@@ -22436,7 +22439,7 @@
         <v>95</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>74</v>
@@ -22447,10 +22450,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22473,17 +22476,17 @@
         <v>84</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>74</v>
@@ -22532,7 +22535,7 @@
         <v>74</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>75</v>
@@ -22547,21 +22550,21 @@
         <v>95</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22667,10 +22670,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22776,16 +22779,16 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="B180" t="s" s="2">
-        <v>624</v>
-      </c>
       <c r="C180" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D180" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
@@ -22804,7 +22807,7 @@
         <v>74</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L180" t="s" s="2">
         <v>129</v>
@@ -22887,13 +22890,13 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D181" t="s" s="2">
         <v>74</v>
@@ -22915,13 +22918,13 @@
         <v>74</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -22998,13 +23001,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>74</v>
@@ -23026,13 +23029,13 @@
         <v>74</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -23109,10 +23112,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23138,16 +23141,16 @@
         <v>103</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>74</v>
@@ -23160,7 +23163,7 @@
         <v>74</v>
       </c>
       <c r="T183" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="U183" t="s" s="2">
         <v>74</v>
@@ -23172,13 +23175,13 @@
         <v>74</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>74</v>
@@ -23196,7 +23199,7 @@
         <v>74</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>75</v>
@@ -23211,21 +23214,21 @@
         <v>95</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23251,13 +23254,13 @@
         <v>103</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -23271,7 +23274,7 @@
         <v>74</v>
       </c>
       <c r="T184" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="U184" t="s" s="2">
         <v>74</v>
@@ -23283,13 +23286,13 @@
         <v>74</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>74</v>
@@ -23307,7 +23310,7 @@
         <v>74</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>75</v>
@@ -23322,21 +23325,21 @@
         <v>95</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AL184" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23362,16 +23365,16 @@
         <v>149</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>74</v>
@@ -23384,7 +23387,7 @@
         <v>74</v>
       </c>
       <c r="T185" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="U185" t="s" s="2">
         <v>74</v>
@@ -23420,7 +23423,7 @@
         <v>74</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>75</v>
@@ -23435,21 +23438,21 @@
         <v>95</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23475,10 +23478,10 @@
         <v>149</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -23493,7 +23496,7 @@
         <v>74</v>
       </c>
       <c r="T186" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="U186" t="s" s="2">
         <v>74</v>
@@ -23529,7 +23532,7 @@
         <v>74</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>75</v>
@@ -23544,25 +23547,25 @@
         <v>95</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AL186" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
@@ -23584,10 +23587,10 @@
         <v>149</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -23602,7 +23605,7 @@
         <v>74</v>
       </c>
       <c r="T187" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="U187" t="s" s="2">
         <v>74</v>
@@ -23638,7 +23641,7 @@
         <v>74</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>75</v>
@@ -23653,25 +23656,25 @@
         <v>95</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AL187" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
@@ -23693,13 +23696,13 @@
         <v>149</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -23713,7 +23716,7 @@
         <v>74</v>
       </c>
       <c r="T188" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="U188" t="s" s="2">
         <v>74</v>
@@ -23749,7 +23752,7 @@
         <v>74</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>75</v>
@@ -23764,21 +23767,21 @@
         <v>95</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AL188" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23804,10 +23807,10 @@
         <v>149</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -23884,10 +23887,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23991,13 +23994,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="B191" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="B191" t="s" s="2">
-        <v>692</v>
-      </c>
       <c r="C191" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D191" t="s" s="2">
         <v>74</v>
@@ -24019,13 +24022,13 @@
         <v>74</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -24102,13 +24105,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>74</v>
@@ -24130,7 +24133,7 @@
         <v>74</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L192" t="s" s="2">
         <v>138</v>
@@ -24213,10 +24216,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -24242,10 +24245,10 @@
         <v>149</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -24269,7 +24272,7 @@
         <v>74</v>
       </c>
       <c r="W193" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="X193" t="s" s="2">
         <v>74</v>
@@ -24296,7 +24299,7 @@
         <v>74</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>75</v>
@@ -24322,14 +24325,14 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
@@ -24351,10 +24354,10 @@
         <v>149</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -24405,7 +24408,7 @@
         <v>74</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>75</v>
@@ -24420,25 +24423,25 @@
         <v>95</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
@@ -24460,10 +24463,10 @@
         <v>149</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -24478,7 +24481,7 @@
         <v>74</v>
       </c>
       <c r="T195" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="U195" t="s" s="2">
         <v>74</v>
@@ -24514,7 +24517,7 @@
         <v>74</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>75</v>
@@ -24529,21 +24532,21 @@
         <v>95</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24569,13 +24572,13 @@
         <v>149</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -24625,7 +24628,7 @@
         <v>74</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>75</v>
@@ -24640,21 +24643,21 @@
         <v>95</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AL196" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24677,17 +24680,17 @@
         <v>84</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>74</v>
@@ -24700,7 +24703,7 @@
         <v>74</v>
       </c>
       <c r="T197" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="U197" t="s" s="2">
         <v>74</v>
@@ -24736,7 +24739,7 @@
         <v>74</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>75</v>
@@ -24751,21 +24754,21 @@
         <v>95</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AL197" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24871,10 +24874,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24982,10 +24985,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -25008,16 +25011,16 @@
         <v>84</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -25067,7 +25070,7 @@
         <v>74</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>75</v>
@@ -25076,27 +25079,27 @@
         <v>83</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AJ200" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AL200" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -25119,23 +25122,23 @@
         <v>84</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q201" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="R201" t="s" s="2">
         <v>74</v>
@@ -25180,7 +25183,7 @@
         <v>74</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>75</v>
@@ -25189,27 +25192,27 @@
         <v>83</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AL201" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM201" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -25232,17 +25235,17 @@
         <v>74</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>74</v>
@@ -25291,7 +25294,7 @@
         <v>74</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>75</v>
@@ -25306,21 +25309,21 @@
         <v>95</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AL202" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -25343,13 +25346,13 @@
         <v>74</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -25400,7 +25403,7 @@
         <v>74</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>75</v>
@@ -25415,10 +25418,10 @@
         <v>95</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AM203" t="s" s="2">
         <v>74</v>
@@ -25426,10 +25429,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25452,19 +25455,19 @@
         <v>74</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>74</v>
@@ -25513,7 +25516,7 @@
         <v>74</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>75</v>
@@ -25528,7 +25531,7 @@
         <v>95</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>74</v>
@@ -25539,10 +25542,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25648,10 +25651,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25759,14 +25762,14 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
@@ -25788,16 +25791,16 @@
         <v>128</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N207" t="s" s="2">
         <v>178</v>
       </c>
       <c r="O207" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>74</v>
@@ -25846,7 +25849,7 @@
         <v>74</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>75</v>
@@ -25872,10 +25875,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25898,19 +25901,19 @@
         <v>74</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>74</v>
@@ -25959,7 +25962,7 @@
         <v>74</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>83</v>
@@ -25974,7 +25977,7 @@
         <v>95</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AL208" t="s" s="2">
         <v>74</v>
@@ -25985,10 +25988,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -26094,10 +26097,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -26205,10 +26208,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -26234,16 +26237,16 @@
         <v>167</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>74</v>
@@ -26292,7 +26295,7 @@
         <v>74</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>75</v>
@@ -26307,21 +26310,21 @@
         <v>95</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL211" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -26427,10 +26430,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26538,10 +26541,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26625,7 +26628,7 @@
         <v>74</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>75</v>
@@ -26640,21 +26643,21 @@
         <v>95</v>
       </c>
       <c r="AK214" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL214" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -26680,13 +26683,13 @@
         <v>149</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
@@ -26736,7 +26739,7 @@
         <v>74</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>75</v>
@@ -26751,21 +26754,21 @@
         <v>95</v>
       </c>
       <c r="AK215" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL215" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26791,14 +26794,14 @@
         <v>103</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>74</v>
@@ -26847,7 +26850,7 @@
         <v>74</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>75</v>
@@ -26862,21 +26865,21 @@
         <v>95</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL216" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26902,14 +26905,14 @@
         <v>149</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>74</v>
@@ -26958,7 +26961,7 @@
         <v>74</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>75</v>
@@ -26973,21 +26976,21 @@
         <v>95</v>
       </c>
       <c r="AK217" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL217" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM217" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -27010,19 +27013,19 @@
         <v>84</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>74</v>
@@ -27071,7 +27074,7 @@
         <v>74</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>75</v>
@@ -27086,21 +27089,21 @@
         <v>95</v>
       </c>
       <c r="AK218" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL218" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM218" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -27126,16 +27129,16 @@
         <v>149</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O219" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P219" t="s" s="2">
         <v>74</v>
@@ -27184,7 +27187,7 @@
         <v>74</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>75</v>
@@ -27199,21 +27202,21 @@
         <v>95</v>
       </c>
       <c r="AK219" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL219" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM219" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -27236,19 +27239,19 @@
         <v>74</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="O220" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>74</v>
@@ -27297,7 +27300,7 @@
         <v>74</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>75</v>
@@ -27312,7 +27315,7 @@
         <v>95</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>74</v>

--- a/docs/StructureDefinition-DIPSRelatedPerson.xlsx
+++ b/docs/StructureDefinition-DIPSRelatedPerson.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:30:20+00:00</t>
+    <t>2026-09-15T05:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSRelatedPerson.xlsx
+++ b/docs/StructureDefinition-DIPSRelatedPerson.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7757" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7757" uniqueCount="805">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T05:06:55+00:00</t>
+    <t>2026-09-17T19:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1713,6 +1713,10 @@
     <t>middlename</t>
   </si>
   <si>
+    <t xml:space="preserve">mellomnavn
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension {http://hl7.no/fhir/StructureDefinition/no-basis-middlename}
 </t>
   </si>
@@ -1990,10 +1994,20 @@
 </t>
   </si>
   <si>
+    <t>The concept of an officially registered address</t>
+  </si>
+  <si>
+    <t>Defines the concept of an officially registered address in Norway. Usually this will be the adress registered in "Folkeregisteret" for persons or "Enhetsregisteret" for organizations.</t>
+  </si>
+  <si>
     <t>RelatedPerson.address.extension:urbanDistrict</t>
   </si>
   <si>
     <t>urbanDistrict</t>
+  </si>
+  <si>
+    <t>bydel
+urban district</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://hl7.no/fhir/StructureDefinition/no-basis-urban-district}
@@ -21238,14 +21252,14 @@
         <v>540</v>
       </c>
       <c r="D166" t="s" s="2">
-        <v>74</v>
+        <v>541</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>74</v>
@@ -21257,13 +21271,13 @@
         <v>74</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -21340,10 +21354,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21369,16 +21383,16 @@
         <v>103</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>74</v>
@@ -21406,10 +21420,10 @@
         <v>257</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>74</v>
@@ -21427,7 +21441,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>75</v>
@@ -21442,21 +21456,21 @@
         <v>95</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21482,16 +21496,16 @@
         <v>149</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>74</v>
@@ -21540,7 +21554,7 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>75</v>
@@ -21555,25 +21569,25 @@
         <v>95</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -21595,13 +21609,13 @@
         <v>149</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -21651,7 +21665,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>75</v>
@@ -21666,25 +21680,25 @@
         <v>95</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
@@ -21706,13 +21720,13 @@
         <v>149</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -21762,7 +21776,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>75</v>
@@ -21777,21 +21791,21 @@
         <v>95</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21817,10 +21831,10 @@
         <v>149</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -21871,7 +21885,7 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>75</v>
@@ -21886,21 +21900,21 @@
         <v>95</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21926,10 +21940,10 @@
         <v>149</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -21980,7 +21994,7 @@
         <v>74</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>75</v>
@@ -21995,21 +22009,21 @@
         <v>95</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22035,14 +22049,14 @@
         <v>297</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>74</v>
@@ -22091,7 +22105,7 @@
         <v>74</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>75</v>
@@ -22106,21 +22120,21 @@
         <v>95</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22143,19 +22157,19 @@
         <v>84</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>74</v>
@@ -22204,7 +22218,7 @@
         <v>74</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>75</v>
@@ -22219,21 +22233,21 @@
         <v>95</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22259,14 +22273,14 @@
         <v>103</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>74</v>
@@ -22294,10 +22308,10 @@
         <v>257</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>74</v>
@@ -22315,7 +22329,7 @@
         <v>74</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>75</v>
@@ -22330,21 +22344,21 @@
         <v>95</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22367,13 +22381,13 @@
         <v>84</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -22424,7 +22438,7 @@
         <v>74</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>75</v>
@@ -22439,7 +22453,7 @@
         <v>95</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>74</v>
@@ -22450,10 +22464,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22476,17 +22490,17 @@
         <v>84</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>74</v>
@@ -22535,7 +22549,7 @@
         <v>74</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>75</v>
@@ -22550,21 +22564,21 @@
         <v>95</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22670,10 +22684,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22779,23 +22793,23 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="B180" t="s" s="2">
-        <v>625</v>
-      </c>
       <c r="C180" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D180" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>74</v>
@@ -22807,13 +22821,13 @@
         <v>74</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>129</v>
+        <v>631</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>130</v>
+        <v>632</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -22890,16 +22904,16 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D181" t="s" s="2">
-        <v>74</v>
+        <v>635</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
@@ -22918,13 +22932,13 @@
         <v>74</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -23001,13 +23015,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>74</v>
@@ -23029,13 +23043,13 @@
         <v>74</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -23112,10 +23126,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23141,16 +23155,16 @@
         <v>103</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>74</v>
@@ -23163,7 +23177,7 @@
         <v>74</v>
       </c>
       <c r="T183" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="U183" t="s" s="2">
         <v>74</v>
@@ -23178,10 +23192,10 @@
         <v>257</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>74</v>
@@ -23199,7 +23213,7 @@
         <v>74</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>75</v>
@@ -23214,21 +23228,21 @@
         <v>95</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23254,13 +23268,13 @@
         <v>103</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -23274,7 +23288,7 @@
         <v>74</v>
       </c>
       <c r="T184" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="U184" t="s" s="2">
         <v>74</v>
@@ -23289,10 +23303,10 @@
         <v>257</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>74</v>
@@ -23310,7 +23324,7 @@
         <v>74</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>75</v>
@@ -23325,21 +23339,21 @@
         <v>95</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL184" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23365,16 +23379,16 @@
         <v>149</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>74</v>
@@ -23387,7 +23401,7 @@
         <v>74</v>
       </c>
       <c r="T185" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="U185" t="s" s="2">
         <v>74</v>
@@ -23423,7 +23437,7 @@
         <v>74</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>75</v>
@@ -23438,21 +23452,21 @@
         <v>95</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23478,10 +23492,10 @@
         <v>149</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -23496,7 +23510,7 @@
         <v>74</v>
       </c>
       <c r="T186" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="U186" t="s" s="2">
         <v>74</v>
@@ -23532,7 +23546,7 @@
         <v>74</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>75</v>
@@ -23547,25 +23561,25 @@
         <v>95</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="AL186" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
@@ -23587,10 +23601,10 @@
         <v>149</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -23605,7 +23619,7 @@
         <v>74</v>
       </c>
       <c r="T187" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="U187" t="s" s="2">
         <v>74</v>
@@ -23641,7 +23655,7 @@
         <v>74</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>75</v>
@@ -23656,25 +23670,25 @@
         <v>95</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="AL187" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
@@ -23696,13 +23710,13 @@
         <v>149</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -23716,7 +23730,7 @@
         <v>74</v>
       </c>
       <c r="T188" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="U188" t="s" s="2">
         <v>74</v>
@@ -23752,7 +23766,7 @@
         <v>74</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>75</v>
@@ -23767,21 +23781,21 @@
         <v>95</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="AL188" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23807,10 +23821,10 @@
         <v>149</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -23887,10 +23901,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23994,13 +24008,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D191" t="s" s="2">
         <v>74</v>
@@ -24022,13 +24036,13 @@
         <v>74</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -24088,13 +24102,13 @@
         <v>76</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>134</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="AL191" t="s" s="2">
         <v>74</v>
@@ -24105,13 +24119,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>74</v>
@@ -24133,7 +24147,7 @@
         <v>74</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="L192" t="s" s="2">
         <v>138</v>
@@ -24216,10 +24230,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -24245,10 +24259,10 @@
         <v>149</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -24272,7 +24286,7 @@
         <v>74</v>
       </c>
       <c r="W193" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="X193" t="s" s="2">
         <v>74</v>
@@ -24299,7 +24313,7 @@
         <v>74</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>75</v>
@@ -24325,14 +24339,14 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
@@ -24354,10 +24368,10 @@
         <v>149</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -24408,7 +24422,7 @@
         <v>74</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>75</v>
@@ -24423,25 +24437,25 @@
         <v>95</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
@@ -24463,10 +24477,10 @@
         <v>149</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -24481,7 +24495,7 @@
         <v>74</v>
       </c>
       <c r="T195" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="U195" t="s" s="2">
         <v>74</v>
@@ -24517,7 +24531,7 @@
         <v>74</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>75</v>
@@ -24532,21 +24546,21 @@
         <v>95</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24572,13 +24586,13 @@
         <v>149</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -24628,7 +24642,7 @@
         <v>74</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>75</v>
@@ -24643,21 +24657,21 @@
         <v>95</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="AL196" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24683,14 +24697,14 @@
         <v>297</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" t="s" s="2">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>74</v>
@@ -24703,7 +24717,7 @@
         <v>74</v>
       </c>
       <c r="T197" t="s" s="2">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="U197" t="s" s="2">
         <v>74</v>
@@ -24739,7 +24753,7 @@
         <v>74</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>75</v>
@@ -24754,21 +24768,21 @@
         <v>95</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AL197" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24874,10 +24888,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24985,10 +24999,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -25011,16 +25025,16 @@
         <v>84</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -25070,7 +25084,7 @@
         <v>74</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>75</v>
@@ -25079,27 +25093,27 @@
         <v>83</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="AJ200" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="AL200" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -25122,23 +25136,23 @@
         <v>84</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q201" t="s" s="2">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="R201" t="s" s="2">
         <v>74</v>
@@ -25183,7 +25197,7 @@
         <v>74</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>75</v>
@@ -25192,27 +25206,27 @@
         <v>83</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="AL201" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM201" t="s" s="2">
-        <v>751</v>
+        <v>755</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -25235,17 +25249,17 @@
         <v>74</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" t="s" s="2">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>74</v>
@@ -25294,7 +25308,7 @@
         <v>74</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>75</v>
@@ -25309,21 +25323,21 @@
         <v>95</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="AL202" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>758</v>
+        <v>762</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -25349,10 +25363,10 @@
         <v>297</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -25403,7 +25417,7 @@
         <v>74</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>75</v>
@@ -25418,10 +25432,10 @@
         <v>95</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="AM203" t="s" s="2">
         <v>74</v>
@@ -25429,10 +25443,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25455,19 +25469,19 @@
         <v>74</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>74</v>
@@ -25516,7 +25530,7 @@
         <v>74</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>75</v>
@@ -25531,7 +25545,7 @@
         <v>95</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>74</v>
@@ -25542,10 +25556,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25651,10 +25665,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25762,14 +25776,14 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
@@ -25791,10 +25805,10 @@
         <v>128</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="N207" t="s" s="2">
         <v>178</v>
@@ -25849,7 +25863,7 @@
         <v>74</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>75</v>
@@ -25875,10 +25889,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25904,16 +25918,16 @@
         <v>264</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>74</v>
@@ -25962,7 +25976,7 @@
         <v>74</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>83</v>
@@ -25977,7 +25991,7 @@
         <v>95</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="AL208" t="s" s="2">
         <v>74</v>
@@ -25988,10 +26002,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -26097,10 +26111,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -26208,10 +26222,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -26321,10 +26335,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -26430,10 +26444,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26541,10 +26555,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26654,10 +26668,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -26765,10 +26779,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26797,7 +26811,7 @@
         <v>199</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
@@ -26876,10 +26890,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26908,7 +26922,7 @@
         <v>207</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
@@ -26987,10 +27001,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -27100,10 +27114,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -27213,10 +27227,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -27242,16 +27256,16 @@
         <v>215</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="O220" t="s" s="2">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>74</v>
@@ -27300,7 +27314,7 @@
         <v>74</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>75</v>
@@ -27315,7 +27329,7 @@
         <v>95</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>74</v>

--- a/docs/StructureDefinition-DIPSRelatedPerson.xlsx
+++ b/docs/StructureDefinition-DIPSRelatedPerson.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T19:39:02+00:00</t>
+    <t>2026-09-18T19:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSRelatedPerson.xlsx
+++ b/docs/StructureDefinition-DIPSRelatedPerson.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T19:41:15+00:00</t>
+    <t>2026-09-29T03:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSRelatedPerson.xlsx
+++ b/docs/StructureDefinition-DIPSRelatedPerson.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T03:57:01+00:00</t>
+    <t>2026-09-29T04:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
